--- a/facerecog/attendance.xlsx
+++ b/facerecog/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,77 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>23:02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14432</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Modi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00:31:40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00:36:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>raghav</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>raghav</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00:34:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vineet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>vineet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00:37:03</t>
         </is>
       </c>
     </row>
